--- a/02--Test-Scenarios--TestCases-Sprint1.xlsx
+++ b/02--Test-Scenarios--TestCases-Sprint1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vignesh\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80166923-DEC8-4A1C-8AAD-F13BABF06B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FD8FBB5-7CE9-4D65-A97E-14D5B04FC549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{426B78D1-5207-4DA6-AE66-C3EC5FCFE94E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{426B78D1-5207-4DA6-AE66-C3EC5FCFE94E}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Scenarios" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1665" uniqueCount="714">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1700" uniqueCount="719">
   <si>
     <t>Scenario ID</t>
   </si>
@@ -1332,9 +1332,6 @@
     <t>Merchant account is created; confirmation/redirect is shown</t>
   </si>
   <si>
-    <t>No response after clicking Finish; account is not created. DOM shows &lt;button type="submit"&gt;Finish&lt;/button&gt; with no bound handler and no console error.</t>
-  </si>
-  <si>
     <t>BUG-001</t>
   </si>
   <si>
@@ -2100,9 +2097,6 @@
     <t>A mandatory-field validation error should be shown for Gender; form should not submit</t>
   </si>
   <si>
-    <t>Page shows an indefinite loading spinner with no error message and no navigation. Reproduced on 3 separate attempts. No error visible in DevTools Console or Network tabs — UI-level hang, not a failed network call.</t>
-  </si>
-  <si>
     <t>Admin Login / Merchant Login</t>
   </si>
   <si>
@@ -2154,9 +2148,6 @@
     <t>No validation error shown; the form proceeds with an invalid phone number</t>
   </si>
   <si>
-    <t>TC_074, TC_105, TC_160_HOW_FIX_IT_LATER</t>
-  </si>
-  <si>
     <t>Commission field on Company Information step accepts values below the documented minimum of 20%</t>
   </si>
   <si>
@@ -2179,13 +2170,37 @@
   </si>
   <si>
     <t>% Executed</t>
+  </si>
+  <si>
+    <t>Page shows an indefinite loading spinner with no error message and no navigation. Reproduced on 3 separate attempts. No error visible in DevTools Console or Network tabs - UI-level hang, not a failed network call.</t>
+  </si>
+  <si>
+    <t>TC_074, TC_105</t>
+  </si>
+  <si>
+    <t>Validation error not shown; minimum 20% is not enforced</t>
+  </si>
+  <si>
+    <t>It is in order</t>
+  </si>
+  <si>
+    <t>A free-text field is appeared to manually enter the company type</t>
+  </si>
+  <si>
+    <t>No response after clicking Finish; account is not created. DOM shows &lt;button type="submit"&gt;Finish&lt;/button&gt; with no handler and no console error.</t>
+  </si>
+  <si>
+    <t>Password field accepts the weak-composition string with no format restriction, but login correctly fails at credential-check stage since no matching Merchant account exists.</t>
+  </si>
+  <si>
+    <t>Page enters an indefinite loading state (spinner) after clicking Register with Gender unselected. Reproduced on 3 attempts. DevTools Network and Console tabs show no failed request and no console error - the UI itself hangs with no validation message and no recovery.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2269,6 +2284,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -2336,7 +2359,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2377,8 +2400,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2391,6 +2412,9 @@
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2808,7 +2832,7 @@
         <v>33</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D6" s="6">
         <v>1</v>
@@ -2825,7 +2849,7 @@
         <v>33</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D7" s="6">
         <v>7</v>
@@ -2842,7 +2866,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D8" s="6">
         <v>6</v>
@@ -2859,7 +2883,7 @@
         <v>33</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D9" s="6">
         <v>3</v>
@@ -2876,7 +2900,7 @@
         <v>33</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D10" s="6">
         <v>9</v>
@@ -2893,7 +2917,7 @@
         <v>33</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D11" s="6">
         <v>8</v>
@@ -2910,7 +2934,7 @@
         <v>33</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D12" s="6">
         <v>7</v>
@@ -2927,7 +2951,7 @@
         <v>33</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D13" s="6">
         <v>3</v>
@@ -2944,7 +2968,7 @@
         <v>33</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D14" s="6">
         <v>2</v>
@@ -2961,7 +2985,7 @@
         <v>33</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D15" s="6">
         <v>3</v>
@@ -2978,7 +3002,7 @@
         <v>33</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D16" s="6">
         <v>2</v>
@@ -2995,7 +3019,7 @@
         <v>298</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D17" s="6">
         <v>1</v>
@@ -3012,7 +3036,7 @@
         <v>298</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D18" s="6">
         <v>8</v>
@@ -3029,7 +3053,7 @@
         <v>335</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D19" s="6">
         <v>3</v>
@@ -3046,7 +3070,7 @@
         <v>335</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D20" s="6">
         <v>6</v>
@@ -3063,7 +3087,7 @@
         <v>335</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D21" s="6">
         <v>10</v>
@@ -3080,7 +3104,7 @@
         <v>335</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D22" s="6">
         <v>6</v>
@@ -3097,7 +3121,7 @@
         <v>335</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D23" s="6">
         <v>1</v>
@@ -3111,10 +3135,10 @@
         <v>26</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D24" s="6">
         <v>4</v>
@@ -3128,10 +3152,10 @@
         <v>27</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D25" s="6">
         <v>1</v>
@@ -3145,10 +3169,10 @@
         <v>28</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D26" s="6">
         <v>1</v>
@@ -3162,10 +3186,10 @@
         <v>29</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D27" s="6">
         <v>12</v>
@@ -3179,10 +3203,10 @@
         <v>30</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D28" s="6">
         <v>1</v>
@@ -3196,10 +3220,10 @@
         <v>31</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D29" s="6">
         <v>1</v>
@@ -3213,10 +3237,10 @@
         <v>32</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D30" s="6">
         <v>8</v>
@@ -3352,7 +3376,7 @@
     <col min="6" max="6" width="64.33203125" customWidth="1"/>
     <col min="7" max="7" width="24.6640625" customWidth="1"/>
     <col min="8" max="8" width="39.5546875" customWidth="1"/>
-    <col min="9" max="9" width="52.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="63.88671875" customWidth="1"/>
     <col min="10" max="10" width="30.44140625" customWidth="1"/>
     <col min="11" max="11" width="8.88671875" customWidth="1"/>
     <col min="12" max="12" width="18.5546875" customWidth="1"/>
@@ -3428,7 +3452,9 @@
       <c r="I2" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="J2" s="5"/>
+      <c r="J2" s="8" t="s">
+        <v>57</v>
+      </c>
       <c r="K2" s="5" t="s">
         <v>35</v>
       </c>
@@ -3468,7 +3494,9 @@
       <c r="I3" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="J3" s="5"/>
+      <c r="J3" s="8" t="s">
+        <v>57</v>
+      </c>
       <c r="K3" s="5" t="s">
         <v>35</v>
       </c>
@@ -3507,7 +3535,9 @@
       <c r="I4" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="J4" s="5"/>
+      <c r="J4" s="8" t="s">
+        <v>57</v>
+      </c>
       <c r="K4" s="5" t="s">
         <v>35</v>
       </c>
@@ -3546,7 +3576,9 @@
       <c r="I5" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="J5" s="5"/>
+      <c r="J5" s="8" t="s">
+        <v>57</v>
+      </c>
       <c r="K5" s="5" t="s">
         <v>35</v>
       </c>
@@ -3585,6 +3617,9 @@
       <c r="I6" t="s">
         <v>90</v>
       </c>
+      <c r="J6" s="8" t="s">
+        <v>57</v>
+      </c>
       <c r="K6" s="5" t="s">
         <v>35</v>
       </c>
@@ -3623,7 +3658,9 @@
       <c r="I7" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="J7" s="5"/>
+      <c r="J7" s="8" t="s">
+        <v>57</v>
+      </c>
       <c r="K7" s="5" t="s">
         <v>35</v>
       </c>
@@ -3660,6 +3697,9 @@
       </c>
       <c r="I8" t="s">
         <v>100</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>57</v>
       </c>
       <c r="K8" s="5" t="s">
         <v>35</v>
@@ -3798,7 +3838,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>9</v>
@@ -3840,7 +3880,7 @@
     </row>
     <row r="13" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>9</v>
@@ -3882,7 +3922,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>9</v>
@@ -3924,7 +3964,7 @@
     </row>
     <row r="15" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>9</v>
@@ -3966,7 +4006,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>9</v>
@@ -4008,7 +4048,7 @@
     </row>
     <row r="17" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>10</v>
@@ -4050,7 +4090,7 @@
     </row>
     <row r="18" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>10</v>
@@ -4092,7 +4132,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>10</v>
@@ -4134,7 +4174,7 @@
     </row>
     <row r="20" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>10</v>
@@ -4176,7 +4216,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>10</v>
@@ -4218,7 +4258,7 @@
     </row>
     <row r="22" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>10</v>
@@ -4260,7 +4300,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>11</v>
@@ -4302,7 +4342,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>11</v>
@@ -4344,7 +4384,7 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>11</v>
@@ -4386,7 +4426,7 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>12</v>
@@ -4428,7 +4468,7 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>12</v>
@@ -4470,7 +4510,7 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>12</v>
@@ -4512,7 +4552,7 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>12</v>
@@ -4554,7 +4594,7 @@
     </row>
     <row r="30" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>12</v>
@@ -4596,7 +4636,7 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>12</v>
@@ -4638,7 +4678,7 @@
     </row>
     <row r="32" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>12</v>
@@ -4680,7 +4720,7 @@
     </row>
     <row r="33" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>12</v>
@@ -4722,7 +4762,7 @@
     </row>
     <row r="34" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>12</v>
@@ -4764,7 +4804,7 @@
     </row>
     <row r="35" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>13</v>
@@ -4806,7 +4846,7 @@
     </row>
     <row r="36" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>13</v>
@@ -4848,7 +4888,7 @@
     </row>
     <row r="37" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>13</v>
@@ -4890,7 +4930,7 @@
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>13</v>
@@ -4932,7 +4972,7 @@
     </row>
     <row r="39" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>13</v>
@@ -4974,7 +5014,7 @@
     </row>
     <row r="40" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>13</v>
@@ -5016,7 +5056,7 @@
     </row>
     <row r="41" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>13</v>
@@ -5058,7 +5098,7 @@
     </row>
     <row r="42" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>13</v>
@@ -5100,7 +5140,7 @@
     </row>
     <row r="43" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>14</v>
@@ -5136,7 +5176,7 @@
         <v>114</v>
       </c>
       <c r="M43" s="12" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="N43" s="6"/>
       <c r="O43" s="6"/>
@@ -5144,7 +5184,7 @@
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>14</v>
@@ -5186,7 +5226,7 @@
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>14</v>
@@ -5228,7 +5268,7 @@
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>14</v>
@@ -5264,7 +5304,7 @@
         <v>114</v>
       </c>
       <c r="M46" s="12" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="N46" s="6"/>
       <c r="O46" s="6"/>
@@ -5272,7 +5312,7 @@
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>14</v>
@@ -5314,7 +5354,7 @@
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>14</v>
@@ -5356,7 +5396,7 @@
     </row>
     <row r="49" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>14</v>
@@ -5398,7 +5438,7 @@
     </row>
     <row r="50" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>15</v>
@@ -5440,7 +5480,7 @@
     </row>
     <row r="51" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>15</v>
@@ -5482,7 +5522,7 @@
     </row>
     <row r="52" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>15</v>
@@ -5524,7 +5564,7 @@
     </row>
     <row r="53" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>16</v>
@@ -5560,7 +5600,7 @@
         <v>107</v>
       </c>
       <c r="M53" s="12" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="N53" s="6"/>
       <c r="O53" s="6"/>
@@ -5568,7 +5608,7 @@
     </row>
     <row r="54" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>16</v>
@@ -5604,7 +5644,7 @@
         <v>131</v>
       </c>
       <c r="M54" s="12" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="N54" s="6"/>
       <c r="O54" s="6"/>
@@ -5612,7 +5652,7 @@
     </row>
     <row r="55" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>17</v>
@@ -5654,7 +5694,7 @@
     </row>
     <row r="56" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>17</v>
@@ -5696,7 +5736,7 @@
     </row>
     <row r="57" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>17</v>
@@ -5738,7 +5778,7 @@
     </row>
     <row r="58" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>18</v>
@@ -5780,7 +5820,7 @@
     </row>
     <row r="59" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>18</v>
@@ -5822,7 +5862,7 @@
     </row>
     <row r="60" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>19</v>
@@ -5864,7 +5904,7 @@
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>20</v>
@@ -5906,7 +5946,7 @@
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>20</v>
@@ -5948,7 +5988,7 @@
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>20</v>
@@ -5984,7 +6024,7 @@
         <v>131</v>
       </c>
       <c r="M63" s="12" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="N63" s="6"/>
       <c r="O63" s="6"/>
@@ -5992,7 +6032,7 @@
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>20</v>
@@ -6034,7 +6074,7 @@
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>20</v>
@@ -6076,7 +6116,7 @@
     </row>
     <row r="66" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>20</v>
@@ -6118,7 +6158,7 @@
     </row>
     <row r="67" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>20</v>
@@ -6160,7 +6200,7 @@
     </row>
     <row r="68" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>20</v>
@@ -6196,7 +6236,7 @@
         <v>144</v>
       </c>
       <c r="M68" s="12" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="N68" s="6"/>
       <c r="O68" s="6"/>
@@ -6204,7 +6244,7 @@
     </row>
     <row r="69" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>21</v>
@@ -6246,7 +6286,7 @@
     </row>
     <row r="70" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>21</v>
@@ -6288,7 +6328,7 @@
     </row>
     <row r="71" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>21</v>
@@ -6330,7 +6370,7 @@
     </row>
     <row r="72" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>22</v>
@@ -6353,7 +6393,9 @@
       <c r="H72" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="I72" s="6"/>
+      <c r="I72" s="12" t="s">
+        <v>352</v>
+      </c>
       <c r="J72" s="8" t="s">
         <v>57</v>
       </c>
@@ -6370,7 +6412,7 @@
     </row>
     <row r="73" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>22</v>
@@ -6393,7 +6435,9 @@
       <c r="H73" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I73" s="6"/>
+      <c r="I73" s="12" t="s">
+        <v>122</v>
+      </c>
       <c r="J73" s="8" t="s">
         <v>57</v>
       </c>
@@ -6410,7 +6454,7 @@
     </row>
     <row r="74" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>22</v>
@@ -6433,7 +6477,9 @@
       <c r="H74" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I74" s="6"/>
+      <c r="I74" s="12" t="s">
+        <v>122</v>
+      </c>
       <c r="J74" s="8" t="s">
         <v>57</v>
       </c>
@@ -6450,7 +6496,7 @@
     </row>
     <row r="75" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>22</v>
@@ -6473,7 +6519,9 @@
       <c r="H75" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I75" s="6"/>
+      <c r="I75" s="12" t="s">
+        <v>472</v>
+      </c>
       <c r="J75" s="10" t="s">
         <v>137</v>
       </c>
@@ -6484,7 +6532,7 @@
         <v>131</v>
       </c>
       <c r="M75" s="12" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="N75" s="6"/>
       <c r="O75" s="6"/>
@@ -6492,7 +6540,7 @@
     </row>
     <row r="76" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>22</v>
@@ -6515,7 +6563,9 @@
       <c r="H76" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I76" s="6"/>
+      <c r="I76" s="12" t="s">
+        <v>122</v>
+      </c>
       <c r="J76" s="8" t="s">
         <v>57</v>
       </c>
@@ -6532,7 +6582,7 @@
     </row>
     <row r="77" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>22</v>
@@ -6555,7 +6605,9 @@
       <c r="H77" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="I77" s="6"/>
+      <c r="I77" s="12" t="s">
+        <v>368</v>
+      </c>
       <c r="J77" s="8" t="s">
         <v>57</v>
       </c>
@@ -6572,7 +6624,7 @@
     </row>
     <row r="78" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>23</v>
@@ -6595,7 +6647,9 @@
       <c r="H78" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="I78" s="6"/>
+      <c r="I78" s="12" t="s">
+        <v>180</v>
+      </c>
       <c r="J78" s="8" t="s">
         <v>57</v>
       </c>
@@ -6612,7 +6666,7 @@
     </row>
     <row r="79" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>23</v>
@@ -6635,7 +6689,9 @@
       <c r="H79" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I79" s="6"/>
+      <c r="I79" s="12" t="s">
+        <v>122</v>
+      </c>
       <c r="J79" s="8" t="s">
         <v>57</v>
       </c>
@@ -6652,7 +6708,7 @@
     </row>
     <row r="80" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>23</v>
@@ -6675,7 +6731,9 @@
       <c r="H80" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I80" s="6"/>
+      <c r="I80" s="12" t="s">
+        <v>122</v>
+      </c>
       <c r="J80" s="8" t="s">
         <v>57</v>
       </c>
@@ -6692,7 +6750,7 @@
     </row>
     <row r="81" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>23</v>
@@ -6715,7 +6773,9 @@
       <c r="H81" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I81" s="6"/>
+      <c r="I81" s="12" t="s">
+        <v>122</v>
+      </c>
       <c r="J81" s="8" t="s">
         <v>57</v>
       </c>
@@ -6732,7 +6792,7 @@
     </row>
     <row r="82" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>23</v>
@@ -6755,7 +6815,9 @@
       <c r="H82" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="I82" s="6"/>
+      <c r="I82" s="12" t="s">
+        <v>385</v>
+      </c>
       <c r="J82" s="8" t="s">
         <v>57</v>
       </c>
@@ -6772,7 +6834,7 @@
     </row>
     <row r="83" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>23</v>
@@ -6795,7 +6857,9 @@
       <c r="H83" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="I83" s="6"/>
+      <c r="I83" s="12" t="s">
+        <v>180</v>
+      </c>
       <c r="J83" s="8" t="s">
         <v>57</v>
       </c>
@@ -6812,7 +6876,7 @@
     </row>
     <row r="84" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>23</v>
@@ -6835,7 +6899,9 @@
       <c r="H84" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I84" s="6"/>
+      <c r="I84" s="12" t="s">
+        <v>122</v>
+      </c>
       <c r="J84" s="8" t="s">
         <v>57</v>
       </c>
@@ -6852,7 +6918,7 @@
     </row>
     <row r="85" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>23</v>
@@ -6875,7 +6941,9 @@
       <c r="H85" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I85" s="6"/>
+      <c r="I85" s="12" t="s">
+        <v>122</v>
+      </c>
       <c r="J85" s="8" t="s">
         <v>57</v>
       </c>
@@ -6892,7 +6960,7 @@
     </row>
     <row r="86" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>23</v>
@@ -6915,7 +6983,9 @@
       <c r="H86" s="6" t="s">
         <v>398</v>
       </c>
-      <c r="I86" s="6"/>
+      <c r="I86" s="12" t="s">
+        <v>713</v>
+      </c>
       <c r="J86" s="10" t="s">
         <v>137</v>
       </c>
@@ -6926,7 +6996,7 @@
         <v>131</v>
       </c>
       <c r="M86" s="12" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="N86" s="6"/>
       <c r="O86" s="6"/>
@@ -6934,7 +7004,7 @@
     </row>
     <row r="87" spans="1:16" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>23</v>
@@ -6957,7 +7027,9 @@
       <c r="H87" s="6" t="s">
         <v>401</v>
       </c>
-      <c r="I87" s="6"/>
+      <c r="I87" s="12" t="s">
+        <v>714</v>
+      </c>
       <c r="J87" s="8" t="s">
         <v>57</v>
       </c>
@@ -6974,7 +7046,7 @@
     </row>
     <row r="88" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>23</v>
@@ -6997,7 +7069,9 @@
       <c r="H88" s="6" t="s">
         <v>405</v>
       </c>
-      <c r="I88" s="6"/>
+      <c r="I88" s="12" t="s">
+        <v>715</v>
+      </c>
       <c r="J88" s="8" t="s">
         <v>57</v>
       </c>
@@ -7014,7 +7088,7 @@
     </row>
     <row r="89" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>24</v>
@@ -7037,7 +7111,9 @@
       <c r="H89" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I89" s="6"/>
+      <c r="I89" s="12" t="s">
+        <v>122</v>
+      </c>
       <c r="J89" s="8" t="s">
         <v>57</v>
       </c>
@@ -7054,7 +7130,7 @@
     </row>
     <row r="90" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>24</v>
@@ -7077,7 +7153,9 @@
       <c r="H90" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I90" s="6"/>
+      <c r="I90" s="12" t="s">
+        <v>122</v>
+      </c>
       <c r="J90" s="8" t="s">
         <v>57</v>
       </c>
@@ -7094,7 +7172,7 @@
     </row>
     <row r="91" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>24</v>
@@ -7117,7 +7195,9 @@
       <c r="H91" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I91" s="6"/>
+      <c r="I91" s="12" t="s">
+        <v>122</v>
+      </c>
       <c r="J91" s="8" t="s">
         <v>57</v>
       </c>
@@ -7134,7 +7214,7 @@
     </row>
     <row r="92" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>24</v>
@@ -7157,7 +7237,9 @@
       <c r="H92" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="I92" s="6"/>
+      <c r="I92" s="12" t="s">
+        <v>180</v>
+      </c>
       <c r="J92" s="8" t="s">
         <v>57</v>
       </c>
@@ -7174,7 +7256,7 @@
     </row>
     <row r="93" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>24</v>
@@ -7197,7 +7279,9 @@
       <c r="H93" s="6" t="s">
         <v>422</v>
       </c>
-      <c r="I93" s="6"/>
+      <c r="I93" s="12" t="s">
+        <v>422</v>
+      </c>
       <c r="J93" s="8" t="s">
         <v>57</v>
       </c>
@@ -7214,7 +7298,7 @@
     </row>
     <row r="94" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>24</v>
@@ -7237,7 +7321,9 @@
       <c r="H94" s="6" t="s">
         <v>425</v>
       </c>
-      <c r="I94" s="6"/>
+      <c r="I94" s="12" t="s">
+        <v>425</v>
+      </c>
       <c r="J94" s="8" t="s">
         <v>57</v>
       </c>
@@ -7254,7 +7340,7 @@
     </row>
     <row r="95" spans="1:16" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>25</v>
@@ -7278,7 +7364,7 @@
         <v>430</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>431</v>
+        <v>716</v>
       </c>
       <c r="J95" s="10" t="s">
         <v>137</v>
@@ -7290,7 +7376,7 @@
         <v>107</v>
       </c>
       <c r="M95" s="12" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="N95" s="6"/>
       <c r="O95" s="6"/>
@@ -7298,30 +7384,32 @@
     </row>
     <row r="96" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D96" s="6" t="s">
         <v>314</v>
       </c>
       <c r="E96" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="F96" s="6" t="s">
         <v>434</v>
       </c>
-      <c r="F96" s="6" t="s">
+      <c r="G96" s="6" t="s">
         <v>435</v>
       </c>
-      <c r="G96" s="6" t="s">
+      <c r="H96" s="6" t="s">
         <v>436</v>
       </c>
-      <c r="H96" s="6" t="s">
-        <v>437</v>
-      </c>
-      <c r="I96" s="6"/>
+      <c r="I96" s="12" t="s">
+        <v>317</v>
+      </c>
       <c r="J96" s="10" t="s">
         <v>137</v>
       </c>
@@ -7332,7 +7420,7 @@
         <v>131</v>
       </c>
       <c r="M96" s="12" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="N96" s="6"/>
       <c r="O96" s="6"/>
@@ -7340,30 +7428,32 @@
     </row>
     <row r="97" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C97" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="E97" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="D97" s="6" t="s">
+      <c r="F97" s="6" t="s">
         <v>438</v>
       </c>
-      <c r="E97" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="F97" s="6" t="s">
+      <c r="G97" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="G97" s="6" t="s">
-        <v>440</v>
-      </c>
       <c r="H97" s="6" t="s">
-        <v>437</v>
-      </c>
-      <c r="I97" s="6"/>
+        <v>436</v>
+      </c>
+      <c r="I97" s="22" t="s">
+        <v>717</v>
+      </c>
       <c r="J97" s="9" t="s">
         <v>57</v>
       </c>
@@ -7380,22 +7470,22 @@
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C98" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="E98" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="D98" s="6" t="s">
+      <c r="F98" s="6" t="s">
         <v>441</v>
-      </c>
-      <c r="E98" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="F98" s="6" t="s">
-        <v>442</v>
       </c>
       <c r="G98" s="6" t="s">
         <v>347</v>
@@ -7403,7 +7493,9 @@
       <c r="H98" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="I98" s="6"/>
+      <c r="I98" s="12" t="s">
+        <v>282</v>
+      </c>
       <c r="J98" s="8" t="s">
         <v>57</v>
       </c>
@@ -7420,22 +7512,22 @@
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C99" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="E99" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="D99" s="6" t="s">
+      <c r="F99" s="6" t="s">
         <v>443</v>
-      </c>
-      <c r="E99" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="F99" s="6" t="s">
-        <v>444</v>
       </c>
       <c r="G99" s="6" t="s">
         <v>347</v>
@@ -7443,7 +7535,9 @@
       <c r="H99" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="I99" s="6"/>
+      <c r="I99" s="12" t="s">
+        <v>282</v>
+      </c>
       <c r="J99" s="8" t="s">
         <v>57</v>
       </c>
@@ -7460,34 +7554,34 @@
     </row>
     <row r="100" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D100" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="E100" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="E100" s="6" t="s">
+      <c r="F100" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="F100" s="6" t="s">
+      <c r="G100" s="6" t="s">
         <v>447</v>
       </c>
-      <c r="G100" s="6" t="s">
+      <c r="H100" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="H100" s="6" t="s">
+      <c r="I100" s="6" t="s">
         <v>449</v>
       </c>
-      <c r="I100" s="6" t="s">
+      <c r="J100" s="11" t="s">
         <v>450</v>
-      </c>
-      <c r="J100" s="11" t="s">
-        <v>451</v>
       </c>
       <c r="K100" s="6" t="s">
         <v>35</v>
@@ -7496,7 +7590,7 @@
         <v>107</v>
       </c>
       <c r="M100" s="6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="N100" s="6"/>
       <c r="O100" s="6"/>
@@ -7504,31 +7598,31 @@
     </row>
     <row r="101" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C101" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="D101" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="D101" s="6" t="s">
+      <c r="E101" s="6" t="s">
         <v>453</v>
       </c>
-      <c r="E101" s="6" t="s">
+      <c r="F101" s="6" t="s">
         <v>454</v>
       </c>
-      <c r="F101" s="6" t="s">
+      <c r="G101" s="6" t="s">
         <v>455</v>
       </c>
-      <c r="G101" s="6" t="s">
+      <c r="H101" s="6" t="s">
         <v>456</v>
       </c>
-      <c r="H101" s="6" t="s">
+      <c r="I101" s="6" t="s">
         <v>457</v>
-      </c>
-      <c r="I101" s="6" t="s">
-        <v>458</v>
       </c>
       <c r="J101" s="8" t="s">
         <v>57</v>
@@ -7546,31 +7640,31 @@
     </row>
     <row r="102" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D102" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="E102" s="6" t="s">
         <v>459</v>
       </c>
-      <c r="E102" s="6" t="s">
+      <c r="F102" s="6" t="s">
         <v>460</v>
       </c>
-      <c r="F102" s="6" t="s">
+      <c r="G102" s="6" t="s">
         <v>461</v>
       </c>
-      <c r="G102" s="6" t="s">
+      <c r="H102" s="6" t="s">
         <v>462</v>
       </c>
-      <c r="H102" s="6" t="s">
-        <v>463</v>
-      </c>
       <c r="I102" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="J102" s="8" t="s">
         <v>57</v>
@@ -7588,31 +7682,31 @@
     </row>
     <row r="103" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D103" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="F103" s="6" t="s">
         <v>464</v>
       </c>
-      <c r="E103" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="F103" s="6" t="s">
+      <c r="G103" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="G103" s="6" t="s">
+      <c r="H103" s="6" t="s">
         <v>466</v>
       </c>
-      <c r="H103" s="6" t="s">
-        <v>467</v>
-      </c>
       <c r="I103" s="6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="J103" s="8" t="s">
         <v>57</v>
@@ -7630,22 +7724,22 @@
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D104" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="E104" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="F104" s="6" t="s">
         <v>468</v>
-      </c>
-      <c r="E104" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="F104" s="6" t="s">
-        <v>469</v>
       </c>
       <c r="G104" s="6" t="s">
         <v>154</v>
@@ -7670,24 +7764,24 @@
       <c r="O104" s="6"/>
       <c r="P104" s="6"/>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:16" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D105" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="E105" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="F105" s="6" t="s">
         <v>470</v>
-      </c>
-      <c r="E105" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="F105" s="6" t="s">
-        <v>471</v>
       </c>
       <c r="G105" s="6" t="s">
         <v>421</v>
@@ -7695,7 +7789,9 @@
       <c r="H105" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="I105" s="6"/>
+      <c r="I105" s="12" t="s">
+        <v>718</v>
+      </c>
       <c r="J105" s="10" t="s">
         <v>137</v>
       </c>
@@ -7706,7 +7802,7 @@
         <v>131</v>
       </c>
       <c r="M105" s="12" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="N105" s="6"/>
       <c r="O105" s="6"/>
@@ -7714,22 +7810,22 @@
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D106" s="6" t="s">
         <v>359</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G106" s="6" t="s">
         <v>361</v>
@@ -7738,7 +7834,7 @@
         <v>122</v>
       </c>
       <c r="I106" s="6" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="J106" s="10" t="s">
         <v>137</v>
@@ -7750,7 +7846,7 @@
         <v>131</v>
       </c>
       <c r="M106" s="12" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="N106" s="6"/>
       <c r="O106" s="6"/>
@@ -7758,19 +7854,19 @@
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F107" s="6" t="s">
         <v>196</v>
@@ -7800,22 +7896,22 @@
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D108" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="E108" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="F108" s="6" t="s">
         <v>476</v>
-      </c>
-      <c r="E108" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="F108" s="6" t="s">
-        <v>477</v>
       </c>
       <c r="G108" s="6" t="s">
         <v>222</v>
@@ -7842,25 +7938,25 @@
     </row>
     <row r="109" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D109" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="E109" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="F109" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="E109" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="F109" s="6" t="s">
+      <c r="G109" s="6" t="s">
         <v>480</v>
-      </c>
-      <c r="G109" s="6" t="s">
-        <v>481</v>
       </c>
       <c r="H109" s="6" t="s">
         <v>122</v>
@@ -7884,25 +7980,25 @@
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D110" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="E110" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="F110" s="6" t="s">
         <v>483</v>
       </c>
-      <c r="E110" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="F110" s="6" t="s">
+      <c r="G110" s="6" t="s">
         <v>484</v>
-      </c>
-      <c r="G110" s="6" t="s">
-        <v>485</v>
       </c>
       <c r="H110" s="6" t="s">
         <v>122</v>
@@ -7926,25 +8022,25 @@
     </row>
     <row r="111" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B111" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D111" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="E111" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="F111" s="6" t="s">
         <v>487</v>
       </c>
-      <c r="E111" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="F111" s="6" t="s">
+      <c r="G111" s="6" t="s">
         <v>488</v>
-      </c>
-      <c r="G111" s="6" t="s">
-        <v>489</v>
       </c>
       <c r="H111" s="6" t="s">
         <v>266</v>
@@ -7968,19 +8064,19 @@
     </row>
     <row r="112" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>290</v>
@@ -7989,10 +8085,10 @@
         <v>54</v>
       </c>
       <c r="H112" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="I112" s="6" t="s">
         <v>492</v>
-      </c>
-      <c r="I112" s="6" t="s">
-        <v>493</v>
       </c>
       <c r="J112" s="9" t="s">
         <v>57</v>
@@ -8010,19 +8106,19 @@
     </row>
     <row r="113" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D113" s="6" t="s">
+        <v>494</v>
+      </c>
+      <c r="E113" s="6" t="s">
         <v>495</v>
-      </c>
-      <c r="E113" s="6" t="s">
-        <v>496</v>
       </c>
       <c r="F113" s="6" t="s">
         <v>276</v>
@@ -8031,10 +8127,10 @@
         <v>277</v>
       </c>
       <c r="H113" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="I113" s="6" t="s">
         <v>497</v>
-      </c>
-      <c r="I113" s="6" t="s">
-        <v>498</v>
       </c>
       <c r="J113" s="8" t="s">
         <v>57</v>
@@ -8052,31 +8148,31 @@
     </row>
     <row r="114" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C114" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="D114" s="6" t="s">
         <v>500</v>
       </c>
-      <c r="D114" s="6" t="s">
+      <c r="E114" s="6" t="s">
         <v>501</v>
       </c>
-      <c r="E114" s="6" t="s">
+      <c r="F114" s="6" t="s">
         <v>502</v>
       </c>
-      <c r="F114" s="6" t="s">
+      <c r="G114" s="6" t="s">
         <v>503</v>
       </c>
-      <c r="G114" s="6" t="s">
+      <c r="H114" s="6" t="s">
         <v>504</v>
       </c>
-      <c r="H114" s="6" t="s">
+      <c r="I114" s="6" t="s">
         <v>505</v>
-      </c>
-      <c r="I114" s="6" t="s">
-        <v>506</v>
       </c>
       <c r="J114" s="8" t="s">
         <v>57</v>
@@ -8094,31 +8190,31 @@
     </row>
     <row r="115" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>32</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>309</v>
       </c>
       <c r="E115" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="F115" s="6" t="s">
         <v>508</v>
-      </c>
-      <c r="F115" s="6" t="s">
-        <v>509</v>
       </c>
       <c r="G115" s="6" t="s">
         <v>312</v>
       </c>
       <c r="H115" s="6" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="I115" s="6" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="J115" s="8" t="s">
         <v>57</v>
@@ -8136,22 +8232,22 @@
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>32</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>305</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="G116" s="6" t="s">
         <v>307</v>
@@ -8178,25 +8274,25 @@
     </row>
     <row r="117" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>32</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>314</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F117" s="6" t="s">
         <v>315</v>
       </c>
       <c r="G117" s="6" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H117" s="6" t="s">
         <v>122</v>
@@ -8220,22 +8316,22 @@
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>32</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G118" s="6" t="s">
         <v>347</v>
@@ -8262,22 +8358,22 @@
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>32</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G119" s="6" t="s">
         <v>347</v>
@@ -8304,31 +8400,31 @@
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>32</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>327</v>
       </c>
       <c r="G120" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="H120" s="6" t="s">
         <v>521</v>
       </c>
-      <c r="H120" s="6" t="s">
-        <v>522</v>
-      </c>
       <c r="I120" s="6" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J120" s="8" t="s">
         <v>57</v>
@@ -8346,31 +8442,31 @@
     </row>
     <row r="121" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A121" s="5" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>32</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D121" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="E121" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="F121" s="6" t="s">
         <v>524</v>
       </c>
-      <c r="E121" s="6" t="s">
-        <v>502</v>
-      </c>
-      <c r="F121" s="6" t="s">
+      <c r="G121" s="6" t="s">
         <v>525</v>
       </c>
-      <c r="G121" s="6" t="s">
+      <c r="H121" s="6" t="s">
         <v>526</v>
       </c>
-      <c r="H121" s="6" t="s">
-        <v>527</v>
-      </c>
       <c r="I121" s="6" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="J121" s="8" t="s">
         <v>57</v>
@@ -8389,7 +8485,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="J9:J121" xr:uid="{8AB1AF88-6067-499E-B353-C2C252CBB4B2}">
+    <dataValidation type="list" allowBlank="1" sqref="J2:J121" xr:uid="{8AB1AF88-6067-499E-B353-C2C252CBB4B2}">
       <formula1>"Pass,Fail,Blocked,Not Executed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -8419,10 +8515,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="13" t="s">
+        <v>656</v>
+      </c>
+      <c r="D1" s="13" t="s">
         <v>657</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>658</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>46</v>
@@ -8431,7 +8527,7 @@
         <v>47</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1" s="13" t="s">
         <v>3</v>
@@ -8440,123 +8536,123 @@
         <v>48</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="66" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>335</v>
       </c>
       <c r="C2" s="12" t="s">
+        <v>660</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>663</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>664</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>665</v>
+      </c>
+      <c r="G2" s="12" t="s">
         <v>661</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>664</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>665</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>666</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>662</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>35</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>33</v>
       </c>
       <c r="C3" s="12" t="s">
+        <v>666</v>
+      </c>
+      <c r="D3" s="12" t="s">
         <v>667</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="E3" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="F3" s="12" t="s">
         <v>668</v>
       </c>
-      <c r="E3" s="12" t="s">
-        <v>671</v>
-      </c>
-      <c r="F3" s="12" t="s">
+      <c r="G3" s="12" t="s">
         <v>669</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>670</v>
       </c>
       <c r="H3" s="12" t="s">
         <v>113</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>33</v>
       </c>
       <c r="C4" s="12" t="s">
+        <v>671</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>672</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="E4" s="12" t="s">
         <v>673</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="F4" s="12" t="s">
         <v>674</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>675</v>
-      </c>
       <c r="G4" s="12" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>113</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>33</v>
       </c>
       <c r="C5" s="12" t="s">
+        <v>679</v>
+      </c>
+      <c r="D5" s="12" t="s">
         <v>680</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="E5" s="12" t="s">
         <v>681</v>
       </c>
-      <c r="E5" s="12" t="s">
-        <v>682</v>
-      </c>
       <c r="F5" s="12" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>113</v>
@@ -8565,170 +8661,170 @@
         <v>113</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="78.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C6" s="12" t="s">
+        <v>683</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>684</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="E6" s="12" t="s">
         <v>685</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>686</v>
-      </c>
       <c r="F6" s="12" t="s">
-        <v>687</v>
+        <v>711</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H6" s="12" t="s">
         <v>35</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B7" s="12" t="s">
+        <v>686</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>687</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>691</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>688</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="F7" s="12" t="s">
         <v>689</v>
       </c>
-      <c r="D7" s="12" t="s">
-        <v>693</v>
-      </c>
-      <c r="E7" s="12" t="s">
+      <c r="G7" s="12" t="s">
         <v>690</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>691</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>692</v>
       </c>
       <c r="H7" s="12" t="s">
         <v>143</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="66" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>298</v>
       </c>
       <c r="C8" s="12" t="s">
+        <v>693</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>694</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>696</v>
+      </c>
+      <c r="F8" s="12" t="s">
         <v>695</v>
       </c>
-      <c r="D8" s="12" t="s">
-        <v>696</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>698</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>697</v>
-      </c>
       <c r="G8" s="12" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H8" s="12" t="s">
         <v>113</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="66" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B9" s="12" t="s">
+        <v>698</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>699</v>
+      </c>
+      <c r="D9" s="12" t="s">
         <v>700</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="E9" s="12" t="s">
         <v>701</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="F9" s="12" t="s">
         <v>702</v>
       </c>
-      <c r="E9" s="12" t="s">
-        <v>703</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>704</v>
-      </c>
       <c r="G9" s="12" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H9" s="12" t="s">
         <v>113</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>335</v>
       </c>
       <c r="C10" s="15" t="s">
+        <v>703</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>704</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>705</v>
+      </c>
+      <c r="F10" s="15" t="s">
         <v>706</v>
       </c>
-      <c r="D10" s="15" t="s">
-        <v>707</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>708</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>709</v>
-      </c>
       <c r="G10" s="15" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H10" s="15" t="s">
         <v>113</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
     </row>
   </sheetData>
@@ -8748,171 +8844,171 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
-        <v>711</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
+      <c r="A1" s="20" t="s">
+        <v>708</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
     </row>
     <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="18" t="s">
-        <v>712</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="18" t="s">
+      <c r="B4" s="16" t="s">
+        <v>709</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="16" t="s">
+        <v>450</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>353</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="18">
+        <v>52</v>
+      </c>
+      <c r="C5" s="18">
+        <v>48</v>
+      </c>
+      <c r="D5" s="18">
+        <v>4</v>
+      </c>
+      <c r="E5" s="18">
+        <v>0</v>
+      </c>
+      <c r="F5" s="18">
+        <v>0</v>
+      </c>
+      <c r="G5" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="B6" s="18">
+        <v>10</v>
+      </c>
+      <c r="C6" s="18">
+        <v>8</v>
+      </c>
+      <c r="D6" s="18">
+        <v>2</v>
+      </c>
+      <c r="E6" s="18">
+        <v>0</v>
+      </c>
+      <c r="F6" s="18">
+        <v>0</v>
+      </c>
+      <c r="G6" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="17" t="s">
+        <v>335</v>
+      </c>
+      <c r="B7" s="18">
+        <v>28</v>
+      </c>
+      <c r="C7" s="18">
+        <v>25</v>
+      </c>
+      <c r="D7" s="18">
+        <v>3</v>
+      </c>
+      <c r="E7" s="18">
+        <v>0</v>
+      </c>
+      <c r="F7" s="18">
+        <v>0</v>
+      </c>
+      <c r="G7" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="17" t="s">
+        <v>432</v>
+      </c>
+      <c r="B8" s="18">
+        <v>6</v>
+      </c>
+      <c r="C8" s="18">
+        <v>4</v>
+      </c>
+      <c r="D8" s="18">
+        <v>1</v>
+      </c>
+      <c r="E8" s="18">
+        <v>1</v>
+      </c>
+      <c r="F8" s="18">
+        <v>0</v>
+      </c>
+      <c r="G8" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="17" t="s">
         <v>451</v>
       </c>
-      <c r="F4" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="20">
-        <v>52</v>
-      </c>
-      <c r="C5" s="20">
-        <v>48</v>
-      </c>
-      <c r="D5" s="20">
-        <v>4</v>
-      </c>
-      <c r="E5" s="20">
+      <c r="B9" s="18">
+        <v>14</v>
+      </c>
+      <c r="C9" s="18">
+        <v>12</v>
+      </c>
+      <c r="D9" s="18">
+        <v>2</v>
+      </c>
+      <c r="E9" s="18">
         <v>0</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F9" s="18">
         <v>0</v>
       </c>
-      <c r="G5" s="21">
+      <c r="G9" s="19">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="19" t="s">
-        <v>298</v>
-      </c>
-      <c r="B6" s="20">
-        <v>10</v>
-      </c>
-      <c r="C6" s="20">
-        <v>8</v>
-      </c>
-      <c r="D6" s="20">
-        <v>2</v>
-      </c>
-      <c r="E6" s="20">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="17" t="s">
+        <v>499</v>
+      </c>
+      <c r="B10" s="18">
+        <v>9</v>
+      </c>
+      <c r="C10" s="18">
+        <v>9</v>
+      </c>
+      <c r="D10" s="18">
         <v>0</v>
       </c>
-      <c r="F6" s="20">
+      <c r="E10" s="18">
         <v>0</v>
       </c>
-      <c r="G6" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="19" t="s">
-        <v>335</v>
-      </c>
-      <c r="B7" s="20">
-        <v>28</v>
-      </c>
-      <c r="C7" s="20">
-        <v>25</v>
-      </c>
-      <c r="D7" s="20">
-        <v>3</v>
-      </c>
-      <c r="E7" s="20">
+      <c r="F10" s="18">
         <v>0</v>
       </c>
-      <c r="F7" s="20">
-        <v>0</v>
-      </c>
-      <c r="G7" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="19" t="s">
-        <v>433</v>
-      </c>
-      <c r="B8" s="20">
-        <v>6</v>
-      </c>
-      <c r="C8" s="20">
-        <v>4</v>
-      </c>
-      <c r="D8" s="20">
-        <v>1</v>
-      </c>
-      <c r="E8" s="20">
-        <v>1</v>
-      </c>
-      <c r="F8" s="20">
-        <v>0</v>
-      </c>
-      <c r="G8" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="19" t="s">
-        <v>452</v>
-      </c>
-      <c r="B9" s="20">
-        <v>14</v>
-      </c>
-      <c r="C9" s="20">
-        <v>12</v>
-      </c>
-      <c r="D9" s="20">
-        <v>2</v>
-      </c>
-      <c r="E9" s="20">
-        <v>0</v>
-      </c>
-      <c r="F9" s="20">
-        <v>0</v>
-      </c>
-      <c r="G9" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="19" t="s">
-        <v>500</v>
-      </c>
-      <c r="B10" s="20">
-        <v>9</v>
-      </c>
-      <c r="C10" s="20">
-        <v>9</v>
-      </c>
-      <c r="D10" s="20">
-        <v>0</v>
-      </c>
-      <c r="E10" s="20">
-        <v>0</v>
-      </c>
-      <c r="F10" s="20">
-        <v>0</v>
-      </c>
-      <c r="G10" s="21">
+      <c r="G10" s="19">
         <v>1</v>
       </c>
     </row>
